--- a/LeaguePost/league_team_01.xlsx
+++ b/LeaguePost/league_team_01.xlsx
@@ -43,36 +43,69 @@
     <t>チームコード</t>
   </si>
   <si>
+    <t>山口大学</t>
+  </si>
+  <si>
+    <t>山口大</t>
+  </si>
+  <si>
+    <t>男子</t>
+  </si>
+  <si>
+    <t>大学</t>
+  </si>
+  <si>
+    <t>準硬式</t>
+  </si>
+  <si>
+    <t>山口県</t>
+  </si>
+  <si>
+    <t>yamadai</t>
+  </si>
+  <si>
+    <t>広島修道大学</t>
+  </si>
+  <si>
+    <t>広修大</t>
+  </si>
+  <si>
+    <t>広島県</t>
+  </si>
+  <si>
+    <t>hirosyu</t>
+  </si>
+  <si>
+    <t>岡山大学</t>
+  </si>
+  <si>
+    <t>岡山大</t>
+  </si>
+  <si>
+    <t>岡山県</t>
+  </si>
+  <si>
+    <t>okadai</t>
+  </si>
+  <si>
+    <t>下関市立大学</t>
+  </si>
+  <si>
+    <t>下市大</t>
+  </si>
+  <si>
+    <t>shimoichi</t>
+  </si>
+  <si>
     <t>広島大学医薬学部</t>
   </si>
   <si>
     <t>広大医</t>
   </si>
   <si>
-    <t>男子</t>
-  </si>
-  <si>
-    <t>大学</t>
-  </si>
-  <si>
-    <t>準硬式</t>
-  </si>
-  <si>
-    <t>広島県</t>
-  </si>
-  <si>
     <t>hiroi</t>
   </si>
   <si>
-    <t>広島修道大学</t>
-  </si>
-  <si>
-    <t>広修大</t>
-  </si>
-  <si>
-    <t>hirosyu</t>
-  </si>
-  <si>
     <t>鳥取大学医学部</t>
   </si>
   <si>
@@ -83,39 +116,6 @@
   </si>
   <si>
     <t>torii</t>
-  </si>
-  <si>
-    <t>山口大学</t>
-  </si>
-  <si>
-    <t>山口大</t>
-  </si>
-  <si>
-    <t>山口県</t>
-  </si>
-  <si>
-    <t>yamadai</t>
-  </si>
-  <si>
-    <t>岡山大学</t>
-  </si>
-  <si>
-    <t>岡山大</t>
-  </si>
-  <si>
-    <t>岡山県</t>
-  </si>
-  <si>
-    <t>okadai</t>
-  </si>
-  <si>
-    <t>下関市立大学</t>
-  </si>
-  <si>
-    <t>下市大</t>
-  </si>
-  <si>
-    <t>shimoichi</t>
   </si>
   <si>
     <t/>
@@ -567,18 +567,18 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
@@ -590,18 +590,18 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -613,7 +613,7 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>24</v>
@@ -636,18 +636,18 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
         <v>27</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
         <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
@@ -659,7 +659,7 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
         <v>31</v>
